--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MISSOURI_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MISSOURI_2012.xlsx
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C125">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C150">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C543">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C743">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C818">
